--- a/DATA/2 GDP მონაცემები.xlsx
+++ b/DATA/2 GDP მონაცემები.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276DE72F-B3AA-4004-AEBD-1BC0B14E9E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="13755" yWindow="75" windowWidth="14760" windowHeight="15405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13755" yWindow="75" windowWidth="14760" windowHeight="15405"/>
   </bookViews>
   <sheets>
     <sheet name="მონაცემები geo" sheetId="1" r:id="rId1"/>
@@ -173,7 +172,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
@@ -228,12 +227,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -424,7 +429,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -461,10 +466,13 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -742,7 +750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1736,7 +1744,7 @@
       <c r="R17" s="14">
         <v>9.6797939261469992</v>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="34">
         <v>7.461614924163996</v>
       </c>
       <c r="U17" s="6"/>
@@ -1796,7 +1804,7 @@
       <c r="R18" s="18">
         <v>9241.4912231148555</v>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="35">
         <v>10296.544362994053</v>
       </c>
       <c r="U18" s="6"/>
@@ -1856,7 +1864,7 @@
       <c r="R19" s="23">
         <v>93022.275315705381</v>
       </c>
-      <c r="S19" s="17">
+      <c r="S19" s="36">
         <v>104598.139883332</v>
       </c>
       <c r="U19" s="6"/>
@@ -2540,7 +2548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
